--- a/nr-update-missing-fields/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T07:52:36+00:00</t>
+    <t>2024-07-17T09:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:13:15+00:00</t>
+    <t>2024-07-17T12:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -404,7 +404,7 @@
     <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source.</t>
   </si>
   <si>
     <t>Organization.meta.versionId</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:12:47+00:00</t>
+    <t>2024-07-17T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:12:21+00:00</t>
+    <t>2024-07-25T07:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
